--- a/docs/sample-output/16-solar-farm/proforma.xlsx
+++ b/docs/sample-output/16-solar-farm/proforma.xlsx
@@ -48,7 +48,7 @@
     <t>Size</t>
   </si>
   <si>
-    <t>1 units</t>
+    <t>50 units</t>
   </si>
   <si>
     <t>Purchase Month</t>
